--- a/resources/templates/standard/F1100-01.xlsx
+++ b/resources/templates/standard/F1100-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">     년 사내/외 교육훈련 계획서</t>
   </si>
@@ -818,9 +821,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -829,28 +834,28 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -921,25 +926,25 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
@@ -953,10 +958,10 @@
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
       <c r="S5" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T5" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -1549,7 +1554,7 @@
       <c r="M31" s="40"/>
       <c r="N31" s="40"/>
       <c r="O31" s="41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P31" s="41"/>
       <c r="Q31" s="41"/>
